--- a/StructureDefinition-research-study-group.xlsx
+++ b/StructureDefinition-research-study-group.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T23:53:55+00:00</t>
+    <t>2025-12-03T18:37:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -352,7 +352,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -636,7 +636,7 @@
     <t>Group.managingEntity</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|RelatedPerson|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1162,7 +1162,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="54.8359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="72.953125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-research-study-group.xlsx
+++ b/StructureDefinition-research-study-group.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T18:37:31+00:00</t>
+    <t>2025-12-03T22:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NCPI FHIR Working Group (http://example.org/example-publisher, ncpi-fhir-ig@googlegroups.com)</t>
+    <t>NCPI FHIR Working Group (https://www.ncpi-acc.org/about/working-groups, ncpi-fhir-ig@googlegroups.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-research-study-group.xlsx
+++ b/StructureDefinition-research-study-group.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T22:26:51+00:00</t>
+    <t>2026-01-13T18:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-research-study-group.xlsx
+++ b/StructureDefinition-research-study-group.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T18:03:13+00:00</t>
+    <t>2026-02-06T18:07:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-research-study-group.xlsx
+++ b/StructureDefinition-research-study-group.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T18:07:39+00:00</t>
+    <t>2026-03-09T20:11:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
